--- a/frontend/public/templates/test_companies.xlsx
+++ b/frontend/public/templates/test_companies.xlsx
@@ -1,135 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="기업등록" state="visible" r:id="rId4"/>
+    <sheet name="기업목록" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
-  <si>
-    <t>기업명</t>
-  </si>
-  <si>
-    <t>사업자등록번호</t>
-  </si>
-  <si>
-    <t>주소</t>
-  </si>
-  <si>
-    <t>지원분야</t>
-  </si>
-  <si>
-    <t>주요제품</t>
-  </si>
-  <si>
-    <t>(주)테스트기업A</t>
-  </si>
-  <si>
-    <t>111-11-11111</t>
-  </si>
-  <si>
-    <t>경기도 성남시 분당구 판교로 123</t>
-  </si>
-  <si>
-    <t>SW 개발</t>
-  </si>
-  <si>
-    <t>AI 솔루션</t>
-  </si>
-  <si>
-    <t>(주)테스트기업B</t>
-  </si>
-  <si>
-    <t>222-22-22222</t>
-  </si>
-  <si>
-    <t>경기도 수원시 영통구 광교로 456</t>
-  </si>
-  <si>
-    <t>디자인</t>
-  </si>
-  <si>
-    <t>UX/UI</t>
-  </si>
-  <si>
-    <t>(주)테스트기업C</t>
-  </si>
-  <si>
-    <t>333-33-33333</t>
-  </si>
-  <si>
-    <t>경기도 용인시 기흥구 흥덕로 789</t>
-  </si>
-  <si>
-    <t>제조</t>
-  </si>
-  <si>
-    <t>자동화장비</t>
-  </si>
-  <si>
-    <t>(주)테스트기업D</t>
-  </si>
-  <si>
-    <t>444-44-44444</t>
-  </si>
-  <si>
-    <t>경기도 고양시 일산동구 장항로 321</t>
-  </si>
-  <si>
-    <t>마케팅</t>
-  </si>
-  <si>
-    <t>광고기획</t>
-  </si>
-  <si>
-    <t>(주)테스트기업E</t>
-  </si>
-  <si>
-    <t>555-55-55555</t>
-  </si>
-  <si>
-    <t>경기도 부천시 원미구 조마루로 654</t>
-  </si>
-  <si>
-    <t>바이오</t>
-  </si>
-  <si>
-    <t>진단키트</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
-      <family val="2"/>
+      <sz val="11"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1A56DB"/>
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -146,22 +56,81 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -240,7 +209,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -275,7 +243,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -310,16 +277,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -441,166 +412,190 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>기업명</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>사업자등록번호</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>소재지</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>주요 사업(지원분야)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>주요 제품</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>(주)뉴테크솔루션</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>6666666666</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구 판교로 200</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>스마트팩토리 솔루션</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>공정 자동화 시스템</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>(주)첨단소재테크</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>7777777777</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>경기도 안양시 동안구 평촌대로 100</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>소재/부품 개발</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>고내열성 합금소재</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>그린에너지(주)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>8888888888</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>경기도 용인시 기흥구 포은대로 50</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>신재생에너지</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>태양광 모듈 시스템</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" t="s">
-        <v>24</v>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>(주)스마트로봇틱스</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>9999999999</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>경기도 화성시 동탄면 기업신도시로 30</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>로봇/자동화</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>协作 로봇 팔</t>
+        </is>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" t="s">
-        <v>29</v>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>카파로보틱스(주)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0123456789</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>경기도 수원시 팔달구 인계로 150</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>로봇 개발</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>물류 로봇</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>